--- a/frontend/public/project_plan_timeline_template.xlsx
+++ b/frontend/public/project_plan_timeline_template.xlsx
@@ -473,10 +473,10 @@
         <v>Calculate total system power budget, select 3.3V/1.8V buck regulators, and size input capacitance.</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-31</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -514,10 +514,10 @@
         <v>Run SPICE simulations for ripple voltage under 2A pulsed load transients.</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-26</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-29</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -555,10 +555,10 @@
         <v>Size bulk electrolytic and ceramic decoupling capacitors for minimal voltage droop.</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-28</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-31</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -596,10 +596,10 @@
         <v>Map all GPIO multiplexing for Cortex-M4 and route high-accuracy 16MHz crystal traces.</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-10-27</v>
+        <v>2026-11-01</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-11-02</v>
+        <v>2026-11-07</v>
       </c>
       <c r="H5">
         <v>6</v>
@@ -637,10 +637,10 @@
         <v>Verify crystal PPM accuracy and load capacitance trimming.</v>
       </c>
       <c r="F6" t="str">
-        <v>2026-10-27</v>
+        <v>2026-11-01</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-04</v>
       </c>
       <c r="H6">
         <v>3</v>
@@ -678,10 +678,10 @@
         <v>Ensure stable logic levels under elevated ambient temperature.</v>
       </c>
       <c r="F7" t="str">
-        <v>2026-10-30</v>
+        <v>2026-11-04</v>
       </c>
       <c r="G7" t="str">
-        <v>2026-11-02</v>
+        <v>2026-11-07</v>
       </c>
       <c r="H7">
         <v>3</v>
@@ -719,10 +719,10 @@
         <v>Formal peer review of BOM cost, power budget, and transceiver protocols.</v>
       </c>
       <c r="F8" t="str">
-        <v>2026-11-03</v>
+        <v>2026-11-08</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-11-04</v>
+        <v>2026-11-09</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -760,10 +760,10 @@
         <v>Model 90 Ohm USB differential pair and 120 Ohm CAN FD transmission lines.</v>
       </c>
       <c r="F9" t="str">
-        <v>2026-11-05</v>
+        <v>2026-11-10</v>
       </c>
       <c r="G9" t="str">
-        <v>2026-11-11</v>
+        <v>2026-11-16</v>
       </c>
       <c r="H9">
         <v>6</v>
@@ -801,10 +801,10 @@
         <v>Simulate return loss and jitter across frequency sweep.</v>
       </c>
       <c r="F10" t="str">
-        <v>2026-11-05</v>
+        <v>2026-11-10</v>
       </c>
       <c r="G10" t="str">
-        <v>2026-11-08</v>
+        <v>2026-11-13</v>
       </c>
       <c r="H10">
         <v>3</v>
@@ -842,10 +842,10 @@
         <v>Verify filter attenuation at 480Mbps harmonic frequencies.</v>
       </c>
       <c r="F11" t="str">
-        <v>2026-11-08</v>
+        <v>2026-11-13</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-11-11</v>
+        <v>2026-11-16</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -883,10 +883,10 @@
         <v>Zero electrical rule check errors, cross-net verification, and netlist export.</v>
       </c>
       <c r="F12" t="str">
-        <v>2026-11-12</v>
+        <v>2026-11-17</v>
       </c>
       <c r="G12" t="str">
-        <v>2026-11-19</v>
+        <v>2026-11-24</v>
       </c>
       <c r="H12">
         <v>7</v>
